--- a/src/pandorafits/formats/nirda/level2_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level2_nirda.xlsx
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1654,12 +1654,12 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAMgVAMZSAMdSAMZ</t>
+          <t>4aCD7UCD4aCD4UCD</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:47</t>
+          <t>HDU checksum updated 2026-01-07T18:04:52</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:47</t>
+          <t>data unit checksum updated 2026-01-07T18:04:52</t>
         </is>
       </c>
     </row>
@@ -1752,41 +1752,49 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>DPCOBSID</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NIRDALevel2HDUList</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DPC Observation ID</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GAIA_ID</t>
+          <t>SEQSTART</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2738188646457069696</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DPC Observation Sequence Start</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
+          <t>NIRDALevel2HDUList</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -1794,13 +1802,13 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIA_ID</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
+          <t>2738188646457069696</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1814,7 +1822,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
+          <t>Cast data to float.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -1828,7 +1836,7 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
+          <t>Applied bias.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -1842,7 +1850,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
+          <t>Applied dark.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1856,10 +1864,38 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
+          <t>Applied flat.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Applied gain.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2072,12 +2108,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KlfjKjeiKjeiKjei</t>
+          <t>JjghLidhJidhJidh</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:23:00</t>
+          <t>HDU checksum updated 2026-01-07T18:05:05</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2131,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:23:00</t>
+          <t>data unit checksum updated 2026-01-07T18:05:05</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3668,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>a05Ib03Ga03Ga03G</t>
+          <t>Zq3Ghn3FZn3Ffn3F</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:23:03</t>
+          <t>HDU checksum updated 2026-01-07T18:05:08</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3691,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:23:03</t>
+          <t>data unit checksum updated 2026-01-07T18:05:08</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3936,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IAahL4XgI9agI9Ug</t>
+          <t>IAafJ1VfI8afI8Uf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:23:03</t>
+          <t>HDU checksum updated 2026-01-07T18:05:08</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3959,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:23:03</t>
+          <t>data unit checksum updated 2026-01-07T18:05:08</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4092,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4654,12 +4690,12 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YddOadcNYdcNadcN</t>
+          <t>WAgCa8ZCZAfCa5ZC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:23:03</t>
+          <t>HDU checksum updated 2026-01-07T18:05:08</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4708,12 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3765800344</t>
+          <t>2105782703</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:23:03</t>
+          <t>data unit checksum updated 2026-01-07T18:05:08</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4828,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4810,7 +4846,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4828,7 +4864,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4940,12 +4976,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>f6Lhf6Iff6Iff6If</t>
+          <t>JngRMkZRJkfRJkZR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:23:03</t>
+          <t>HDU checksum updated 2026-01-07T18:05:17</t>
         </is>
       </c>
     </row>
@@ -4958,12 +4994,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3392536972</t>
+          <t>3839371503</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:23:03</t>
+          <t>data unit checksum updated 2026-01-07T18:05:17</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5226,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.5136559477014376</t>
+          <t>0.9300590780316826</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5208,7 +5244,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2941.8889239898053</t>
+          <t>653.2973192947069</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5240,7 +5276,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.012166400269627292</t>
+          <t>0.012166400269627294</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -5268,7 +5304,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1959.1480628736472</t>
+          <t>1959.148062873647</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -5368,12 +5404,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1afI2af91afG1af9</t>
+          <t>9pAG9n299n9E9n99</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:23:03</t>
+          <t>HDU checksum updated 2026-01-07T18:05:17</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5422,12 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1310739</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:23:03</t>
+          <t>data unit checksum updated 2026-01-07T18:05:17</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5660,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GYiEGVgEGVgEGVgE</t>
+          <t>FYhHFXfFFXfFFXfF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:23:07</t>
+          <t>HDU checksum updated 2026-01-07T18:05:21</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5683,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:23:07</t>
+          <t>data unit checksum updated 2026-01-07T18:05:21</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level2_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level2_nirda.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext5" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext6" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext8" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +547,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>MODEL_IMAGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -561,16 +562,287 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C9" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ImageHDU</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NAXIS3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>electrons/pixel</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>data units: electrons/pixel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DZfIGXeFDXeFDXeF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-08T14:09:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1579659438</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-08T14:09:24</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -584,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,7 +1134,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.01</t>
+          <t>v2.08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -898,7 +1170,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1378,7 +1650,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INTEGRTS</t>
+          <t>GRPS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1389,14 +1661,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SC_Integrations value for acquire</t>
+          <t>SC_Groups value for acquire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EXPOSRES</t>
+          <t>INTEGRTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1407,32 +1679,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SC_Exposures value for acquire</t>
+          <t>SC_Integrations value for acquire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENDDELAY</t>
+          <t>EXPOSRES</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SC_EndDelay value for acquire</t>
+          <t>SC_Exposures value for acquire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RSTSINC</t>
+          <t>ENDDELAY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1443,14 +1715,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Reset frames included in datacube?</t>
+          <t>SC_EndDelay value for acquire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DRPSINC</t>
+          <t>RSTSINC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1461,50 +1733,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Drop frames included in datacube?</t>
+          <t>Reset frames included in datacube?</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FRMSTOT</t>
+          <t>DRPSINC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Total #frames clocked in acquire</t>
+          <t>Drop frames included in datacube?</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FRMSEXP</t>
+          <t>FRMSTOT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>#frames expected to be acquired from MACIE/SIDE</t>
+          <t>Total #frames clocked in acquire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FRMSACQ</t>
+          <t>FRMSEXP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1515,208 +1787,208 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>#frames actually acquired from  MACIE/SIDECAR</t>
+          <t>#frames expected to be acquired from MACIE/SIDE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GRPSAVGD</t>
+          <t>FRMSACQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Whether groups were averaged (1) or not (0)</t>
+          <t>#frames actually acquired from  MACIE/SIDECAR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PAMPGAIN</t>
+          <t>GRPSAVGD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pre-amp gain based on gain register value.</t>
+          <t>Whether groups were averaged (1) or not (0)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FRMTIME</t>
+          <t>PAMPGAIN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Frame time in ms</t>
+          <t>Pre-amp gain based on gain register value.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TSIDECAR</t>
+          <t>FRMTIME</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>999.0</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SIDECAR Temperature at start of integration</t>
+          <t>Frame time in ms</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TCOMPRJT</t>
+          <t>TSIDECAR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>297.6682434082031</t>
+          <t>999.0</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CCE Compressor Reject Temperature at start of i</t>
+          <t>SIDECAR Temperature at start of integration</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TCLDTIP1</t>
+          <t>TCOMPRJT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>78.88285064697266</t>
+          <t>297.6682434082031</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CCE Cold Tip1 Temperature at start of integrati</t>
+          <t>CCE Compressor Reject Temperature at start of i</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TCLDTIP2</t>
+          <t>TCLDTIP1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>68.87708282470703</t>
+          <t>78.88285064697266</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CCE Cold Tip2 Temperature at start of integrati</t>
+          <t>CCE Cold Tip1 Temperature at start of integrati</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>TCLDTIP2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>4aCD7UCD4aCD4UCD</t>
+          <t>68.87708282470703</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:04:52</t>
+          <t>CCE Cold Tip2 Temperature at start of integrati</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>iX54lU44iU44iU44</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:04:52</t>
+          <t>HDU checksum updated 2026-01-08T14:08:56</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.4.2</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-08T14:08:56</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TARG_RA</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Target right ascension [deg]</t>
-        </is>
-      </c>
+          <t>0.4.2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TARG_DEC</t>
+          <t>TARG_RA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1727,88 +1999,92 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Target declination [deg]</t>
+          <t>Target right ascension [deg]</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TARG_RLL</t>
+          <t>TARG_DEC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Commanded roll [deg]</t>
+          <t>Target declination [deg]</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DPCOBSID</t>
+          <t>TARG_RLL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DPC Observation ID</t>
+          <t>Commanded roll [deg]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEQSTART</t>
+          <t>DPCOBSID</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DPC Observation Sequence Start</t>
+          <t>DPC Observation ID</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>SEQSTART</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NIRDALevel2HDUList</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>2454833</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DPC Observation Sequence Start</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GAIA_ID</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2738188646457069696</t>
+          <t>NIRDALevel2HDUList</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1816,27 +2092,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>PFTIME</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>2026-01-08T19:08:56.216</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIA_ID</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
+          <t>2738188646457069696</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -1850,7 +2130,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
+          <t>Cast data to float.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1864,7 +2144,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
+          <t>Applied bias.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -1878,7 +2158,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
+          <t>Applied dark.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -1892,10 +2172,38 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
+          <t>Applied flat.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Applied gain.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2108,12 +2416,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JjghLidhJidhJidh</t>
+          <t>IjehJichIichIich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:05:05</t>
+          <t>HDU checksum updated 2026-01-08T14:09:09</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2439,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:05:05</t>
+          <t>data unit checksum updated 2026-01-08T14:09:09</t>
         </is>
       </c>
     </row>
@@ -3668,12 +3976,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zq3Ghn3FZn3Ffn3F</t>
+          <t>Z23Ke11HZ11Hd11H</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:05:08</t>
+          <t>HDU checksum updated 2026-01-08T14:09:12</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3999,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:05:08</t>
+          <t>data unit checksum updated 2026-01-08T14:09:12</t>
         </is>
       </c>
     </row>
@@ -3936,12 +4244,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IAafJ1VfI8afI8Uf</t>
+          <t>GAajJ5ThGAYhG5Yh</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:05:08</t>
+          <t>HDU checksum updated 2026-01-08T14:09:12</t>
         </is>
       </c>
     </row>
@@ -3959,7 +4267,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:05:08</t>
+          <t>data unit checksum updated 2026-01-08T14:09:12</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4998,12 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WAgCa8ZCZAfCa5ZC</t>
+          <t>Yd3Tac2TYc2Tac2T</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:05:08</t>
+          <t>HDU checksum updated 2026-01-08T14:09:12</t>
         </is>
       </c>
     </row>
@@ -4708,12 +5016,12 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2105782703</t>
+          <t>3727981219</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:05:08</t>
+          <t>data unit checksum updated 2026-01-08T14:09:12</t>
         </is>
       </c>
     </row>
@@ -4976,12 +5284,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JngRMkZRJkfRJkZR</t>
+          <t>9AfGA6eE2AeE93eE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:05:17</t>
+          <t>HDU checksum updated 2026-01-08T14:09:20</t>
         </is>
       </c>
     </row>
@@ -4994,12 +5302,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3839371503</t>
+          <t>3098569257</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:05:17</t>
+          <t>data unit checksum updated 2026-01-08T14:09:20</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5057,7 +5365,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5377,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5155,7 +5463,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -5180,254 +5488,1264 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>APERTURE</t>
-        </is>
-      </c>
+          <t>WCSAXES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONTAM</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Flux not from the target in aperture in e/s</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMPLTE</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9300590780316826</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fraction of flux from the target in aperture</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOTAP</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>653.2973192947069</t>
+          <t>-0.76604444311898</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Total flux expected in aperture in e/s</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>359.9895610861746</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-0.64278760968654</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.012166400269627294</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>-0.64278760968654</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ROW</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1030.7973568522598</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>0.76604444311898</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COLUMN</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1959.148062873647</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-0.00033055555555555</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GAIA_ID</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2738188646457069696</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>0.00033055555555556</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IMSIZE0</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Size of the full detector image in ROW</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IMCRNR0</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Corner of the image in ROW.</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IMSIZE1</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>RA---TAN-SIP</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Size of the full detector image in COLUMN</t>
+          <t>TAN (gnomonic) projection + SIP distortions</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IMCRNR1</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>DEC--TAN-SIP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Corner of the image in COLUMN.</t>
+          <t>TAN (gnomonic) projection + SIP distortions</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9pAG9n299n9E9n99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:05:17</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:05:17</t>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LONPOLE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[deg] Native longitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LATPOLE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[deg] Native latitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MJDREF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[d] MJD of fiducial time</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RADESYS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Equatorial coordinate system</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A_ORDER</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 0, detector to sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A_0_0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1.43968385103818e-18</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A_0_1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8.33080849385211e-20</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A_0_2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-2.0774269923818e-22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A_0_3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>-6.1942239971391e-24</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A_1_0</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-1.6079633450868e-05</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A_1_1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-2.296309635005e-06</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A_1_2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-2.5446960820262e-09</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A_2_0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-1.3376524471463e-22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A_2_1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-4.7146403712976e-24</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A_3_0</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-2.7620538848694e-09</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B_ORDER</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 1, detector to sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>B_0_0</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5.46848630496921e-05</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B_0_1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.000544760966309473</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B_0_2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.78045904395735e-05</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B_0_3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8.38474933780047e-10</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B_1_0</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>-7.535285644557e-20</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B_1_1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>-2.5856386119289e-20</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B_1_2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>-1.3106781614018e-23</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B_2_0</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4.0102324001493e-05</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B_2_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6.04776564999714e-10</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B_3_0</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-1.8459105666067e-23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AP_ORDER</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 0, sky to detector</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AP_0_0</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-1.4396838510381e-18</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AP_0_1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-8.3308084938521e-20</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AP_0_2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2.07742699238182e-22</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AP_0_3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6.19422399713915e-24</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AP_1_0</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.60796334508681e-05</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AP_1_1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2.29630963500504e-06</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AP_1_2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2.54469608202621e-09</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AP_2_0</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.33765244714635e-22</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AP_2_1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4.71464037129765e-24</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AP_3_0</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2.76205388486941e-09</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BP_ORDER</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 1, sky to detector</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BP_0_0</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-5.4684863049692e-05</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BP_0_1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-0.00054476096630947</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BP_0_2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-3.7804590439573e-05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BP_0_3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-8.3847493378004e-10</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BP_1_0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>7.53528564455708e-20</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BP_1_1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2.5856386119289e-20</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BP_1_2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1.31067816140184e-23</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BP_2_0</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>-4.0102324001493e-05</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BP_2_1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>-6.0477656499971e-10</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BP_3_0</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1.84591056660678e-23</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>nPAEqM5DnMADnM3D</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-08T14:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1698318627</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-08T14:09:21</t>
         </is>
       </c>
     </row>
@@ -5442,7 +6760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5497,17 +6815,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -5519,17 +6837,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -5545,7 +6863,11 @@
           <t>2048</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5559,131 +6881,299 @@
           <t>2048</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAXIS3</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>CONTAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>electrons/pixel</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>data units: electrons/pixel</t>
+          <t>Flux not from the target in aperture in e/s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
+          <t>COMPLTE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>0.8298230297620204</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>Fraction of flux from the target in aperture</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>TOTAP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FYhHFXfFFXfFFXfF</t>
+          <t>582.8889515060163</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:05:21</t>
+          <t>Total flux expected in aperture in e/s</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1579659438</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-07T18:05:21</t>
+          <t>359.98956765457893</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.01225927433994913</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ROW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1031.0244642272605</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1958.982650600545</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GAIA_ID</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2738188646457069696</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5l9JAk6I5k6IAk6I</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-08T14:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-08T14:09:21</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level2_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level2_nirda.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext6" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext7" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext8" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext9" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +587,21 @@
         </is>
       </c>
       <c r="C10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WAVELENGTH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TableHDU</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -818,12 +834,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DZfIGXeFDXeFDXeF</t>
+          <t>GXjGHXgFGXgFGXgF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:09:24</t>
+          <t>HDU checksum updated 2026-01-16T10:21:27</t>
         </is>
       </c>
     </row>
@@ -841,7 +857,397 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:09:24</t>
+          <t>data unit checksum updated 2026-01-16T10:21:27</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TABLE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TABLE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ASCII table extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of dimension 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of group parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TFIELDS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TTYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>wavelength</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>wavelength</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TUNIT1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>micron</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TBCOL1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sensitivity</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sensitivity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D25.17</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TUNIT2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cm2 Angstrom electron / (erg pix)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TBCOL2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WAVELENGTH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>WAVELENGTH</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DPDbFPDZDPDbDPDZ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-16T10:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3437370878</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T10:21:28</t>
         </is>
       </c>
     </row>
@@ -1944,12 +2350,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>iX54lU44iU44iU44</t>
+          <t>6YWi7WVg6WVg6WVg</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:56</t>
+          <t>HDU checksum updated 2026-01-16T10:20:58</t>
         </is>
       </c>
     </row>
@@ -1967,7 +2373,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:56</t>
+          <t>data unit checksum updated 2026-01-16T10:20:58</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2448,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DPCOBSID</t>
+          <t>DPCSEQID</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2053,7 +2459,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DPC Observation ID</t>
+          <t>DPC Obseravation Sequence ID</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2504,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-01-08T19:08:56.216</t>
+          <t>2026-01-16T17:20:58.449</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2416,12 +2822,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IjehJichIichIich</t>
+          <t>KmhkMkejKkejKkej</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:09:09</t>
+          <t>HDU checksum updated 2026-01-16T10:21:11</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2845,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:09:09</t>
+          <t>data unit checksum updated 2026-01-16T10:21:11</t>
         </is>
       </c>
     </row>
@@ -3976,12 +4382,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Z23Ke11HZ11Hd11H</t>
+          <t>a14Jd14Ha14Ha14H</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:09:12</t>
+          <t>HDU checksum updated 2026-01-16T10:21:14</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4405,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:09:12</t>
+          <t>data unit checksum updated 2026-01-16T10:21:14</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4650,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GAajJ5ThGAYhG5Yh</t>
+          <t>JAaiK6XhJAahJ3Wh</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:09:12</t>
+          <t>HDU checksum updated 2026-01-16T10:21:14</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4673,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:09:12</t>
+          <t>data unit checksum updated 2026-01-16T10:21:14</t>
         </is>
       </c>
     </row>
@@ -4998,12 +5404,12 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yd3Tac2TYc2Tac2T</t>
+          <t>Zc7Vfc4SZc4Sdc4S</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:09:12</t>
+          <t>HDU checksum updated 2026-01-16T10:21:14</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5427,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:09:12</t>
+          <t>data unit checksum updated 2026-01-16T10:21:14</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5690,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9AfGA6eE2AeE93eE</t>
+          <t>5AjEA4gE8AgEA3gE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:09:20</t>
+          <t>HDU checksum updated 2026-01-16T10:21:23</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5713,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:09:20</t>
+          <t>data unit checksum updated 2026-01-16T10:21:23</t>
         </is>
       </c>
     </row>
@@ -6722,12 +7128,12 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>nPAEqM5DnMADnM3D</t>
+          <t>1OAE2M9D1MAD1M9D</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:09:21</t>
+          <t>HDU checksum updated 2026-01-16T10:21:23</t>
         </is>
       </c>
     </row>
@@ -6745,7 +7151,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:09:21</t>
+          <t>data unit checksum updated 2026-01-16T10:21:23</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7556,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5l9JAk6I5k6IAk6I</t>
+          <t>9kAICk2I9k9IAk9I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:09:21</t>
+          <t>HDU checksum updated 2026-01-16T10:21:23</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7579,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:09:21</t>
+          <t>data unit checksum updated 2026-01-16T10:21:23</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level2_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level2_nirda.xlsx
@@ -17,7 +17,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext6" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext7" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext9" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +487,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASTROMETRY</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -503,12 +502,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -518,12 +517,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CATALOG</t>
+          <t>PRF_MODEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -533,7 +532,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>MODEL_IMAGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -548,7 +547,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MODEL_IMAGE</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -563,12 +562,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C9" t="b">
@@ -578,30 +577,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>WAVELENGTH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>TableHDU</t>
         </is>
       </c>
       <c r="C10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WAVELENGTH</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TableHDU</t>
-        </is>
-      </c>
-      <c r="C11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -616,262 +600,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Example Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XTENSION</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Image extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BITPIX</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>array data type</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NAXIS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>number of array dimensions</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NAXIS1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NAXIS2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NAXIS3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>number of parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>electrons/pixel</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>data units: electrons/pixel</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GXjGHXgFGXgFGXgF</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:21:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1579659438</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:21:27</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1224,12 +952,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DPDbFPDZDPDbDPDZ</t>
+          <t>DPFaENCYDNCaDNCW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:21:28</t>
+          <t>HDU checksum updated 2026-01-16T15:41:37</t>
         </is>
       </c>
     </row>
@@ -1247,7 +975,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:21:28</t>
+          <t>data unit checksum updated 2026-01-16T15:41:37</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2078,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>6YWi7WVg6WVg6WVg</t>
+          <t>9YYe9VXe9VXe9VXe</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:20:58</t>
+          <t>HDU checksum updated 2026-01-16T15:41:09</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2101,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:20:58</t>
+          <t>data unit checksum updated 2026-01-16T15:41:09</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2232,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-01-16T17:20:58.449</t>
+          <t>2026-01-16T22:41:09.242</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2822,12 +2550,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KmhkMkejKkejKkej</t>
+          <t>KlgjLiehKiehKieh</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:21:11</t>
+          <t>HDU checksum updated 2026-01-16T15:41:21</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2573,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:21:11</t>
+          <t>data unit checksum updated 2026-01-16T15:41:21</t>
         </is>
       </c>
     </row>
@@ -4026,7 +3754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4059,17 +3787,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -4081,17 +3809,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -4113,7 +3841,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -4126,12 +3854,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of dimension 1</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -4144,12 +3872,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -4167,7 +3895,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
@@ -4192,39 +3920,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>BSCALE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of table fields</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
+          <t>BZERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -4232,180 +3956,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>J9ahJ9WfJ9afJ9Wf</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-16T15:41:24</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>a14Jd14Ha14Ha14H</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:21:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:21:14</t>
+          <t>4292739037</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:41:24</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4453,17 +4055,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -4475,17 +4077,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4109,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -4520,12 +4122,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 1</t>
         </is>
       </c>
     </row>
@@ -4538,12 +4140,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 2</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4163,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -4586,35 +4188,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSCALE</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BZERO</t>
+          <t>TTYPE1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -4622,58 +4228,540 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFORM1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JAaiK6XhJAahJ3Wh</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:21:14</t>
-        </is>
-      </c>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>phot_g_mean_flux</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>phot_g_mean_flux</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>phot_bp_mean_flux</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>phot_bp_mean_flux</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>phot_rp_mean_flux</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>phot_rp_mean_flux</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>j_flux</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>j_flux</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>h_flux</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_flux</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>k_flux</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>k_flux</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>teff_gspphot</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>teff_gspphot</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>row0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>row0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TTYPE14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>column0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>column0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TFORM14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Zb6Rea4RZa4Rda4R</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-16T15:41:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4292739037</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:21:14</t>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3727981219</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:41:24</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4721,17 +4809,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -4743,17 +4831,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -4765,17 +4853,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -4788,12 +4876,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of dimension 1</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -4806,628 +4894,160 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>NAXIS3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PRF_MODEL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>PRF_MODEL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DPOS0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Change in position in Row from original WCS.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
+          <t>DPOS1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Change in position in Column from original WCS.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>5AiDA1gC78gCA8gC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-16T15:41:33</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TTYPE6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TFORM6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TTYPE7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TFORM7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TTYPE8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TFORM8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TTYPE9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TFORM9</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TTYPE10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TFORM10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TTYPE11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TFORM11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TTYPE12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TFORM12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TTYPE13</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TFORM13</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TTYPE14</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TFORM14</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Zc7Vfc4SZc4Sdc4S</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:21:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>3727981219</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:21:14</t>
+          <t>3098569257</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:41:33</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5485,7 +5105,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5139,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5572,148 +5192,1300 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAXIS3</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PRF_MODEL</t>
-        </is>
-      </c>
+          <t>CRPIX1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>2008.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DPOS0</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Change in position in Row from original WCS.</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DPOS1</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.76604444311898</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Change in position in Column from original WCS.</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5AjEA4gE8AgEA3gE</t>
+          <t>-0.64278760968654</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:21:23</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3098569257</t>
+          <t>-0.64278760968654</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:21:23</t>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PC2_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.76604444311898</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CDELT1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-0.00033055555555555</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CDELT2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.00033055555555556</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CUNIT1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CUNIT2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CTYPE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RA---TAN-SIP</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TAN (gnomonic) projection + SIP distortions</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CTYPE2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEC--TAN-SIP</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TAN (gnomonic) projection + SIP distortions</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CRVAL1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CRVAL2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LONPOLE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[deg] Native longitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LATPOLE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[deg] Native latitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MJDREF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[d] MJD of fiducial time</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RADESYS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Equatorial coordinate system</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A_ORDER</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 0, detector to sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A_0_0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1.43968385103818e-18</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A_0_1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8.33080849385211e-20</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A_0_2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-2.0774269923818e-22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A_0_3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>-6.1942239971391e-24</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A_1_0</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-1.6079633450868e-05</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A_1_1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-2.296309635005e-06</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A_1_2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-2.5446960820262e-09</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A_2_0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-1.3376524471463e-22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A_2_1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-4.7146403712976e-24</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A_3_0</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-2.7620538848694e-09</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B_ORDER</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 1, detector to sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>B_0_0</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5.46848630496921e-05</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B_0_1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.000544760966309473</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B_0_2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.78045904395735e-05</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B_0_3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8.38474933780047e-10</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B_1_0</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>-7.535285644557e-20</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B_1_1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>-2.5856386119289e-20</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B_1_2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>-1.3106781614018e-23</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B_2_0</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4.0102324001493e-05</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B_2_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6.04776564999714e-10</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B_3_0</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-1.8459105666067e-23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AP_ORDER</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 0, sky to detector</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AP_0_0</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-1.4396838510381e-18</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AP_0_1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-8.3308084938521e-20</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AP_0_2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2.07742699238182e-22</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AP_0_3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6.19422399713915e-24</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AP_1_0</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.60796334508681e-05</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AP_1_1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2.29630963500504e-06</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AP_1_2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2.54469608202621e-09</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AP_2_0</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.33765244714635e-22</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AP_2_1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4.71464037129765e-24</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AP_3_0</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2.76205388486941e-09</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BP_ORDER</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SIP polynomial order, axis 1, sky to detector</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BP_0_0</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-5.4684863049692e-05</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BP_0_1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-0.00054476096630947</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BP_0_2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-3.7804590439573e-05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BP_0_3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-8.3847493378004e-10</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BP_1_0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>7.53528564455708e-20</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BP_1_1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2.5856386119289e-20</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BP_1_2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1.31067816140184e-23</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BP_2_0</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>-4.0102324001493e-05</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BP_2_1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>-6.0477656499971e-10</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BP_3_0</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1.84591056660678e-23</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1NBD1K9B1KAB1K7B</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-16T15:41:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1698318627</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:41:33</t>
         </is>
       </c>
     </row>
@@ -5728,7 +6500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5771,7 +6543,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -5783,12 +6555,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5869,7 +6641,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
@@ -5894,1264 +6666,254 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Number of coordinate axes</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
+          <t>CONTAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2008.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Flux not from the target in aperture in e/s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CRPIX2</t>
+          <t>COMPLTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>0.8298230297620204</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Fraction of flux from the target in aperture</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PC1_1</t>
+          <t>TOTAP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.76604444311898</t>
+          <t>582.8889515060163</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>Total flux expected in aperture in e/s</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PC1_2</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
+          <t>359.98956765457893</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PC2_1</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
+          <t>0.01225927433994913</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PC2_2</t>
+          <t>ROW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.76604444311898</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
+          <t>1031.0244642272605</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CDELT1</t>
+          <t>COLUMN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.00033055555555555</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
+          <t>1958.982650600545</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CDELT2</t>
+          <t>GAIA_ID</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.00033055555555556</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
+          <t>2738188646457069696</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CUNIT1</t>
+          <t>IMSIZE0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>Size of the full detector image in ROW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CUNIT2</t>
+          <t>IMCRNR0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>Corner of the image in ROW.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CTYPE1</t>
+          <t>IMSIZE1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RA---TAN-SIP</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
+          <t>Size of the full detector image in COLUMN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CTYPE2</t>
+          <t>IMCRNR1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DEC--TAN-SIP</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
+          <t>Corner of the image in COLUMN.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRVAL1</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9j9HBi9G9i9GAi9G</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>HDU checksum updated 2026-01-16T15:41:33</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CRVAL2</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LONPOLE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[deg] Native longitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LATPOLE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>[deg] Native latitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MJDREF</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>[d] MJD of fiducial time</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RADESYS</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ICRS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Equatorial coordinate system</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A_ORDER</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 0, detector to sky</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A_0_0</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1.43968385103818e-18</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A_0_1</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>8.33080849385211e-20</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A_0_2</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-2.0774269923818e-22</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A_0_3</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>-6.1942239971391e-24</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A_1_0</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-1.6079633450868e-05</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A_1_1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-2.296309635005e-06</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A_1_2</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>-2.5446960820262e-09</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A_2_0</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-1.3376524471463e-22</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A_2_1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>-4.7146403712976e-24</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A_3_0</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-2.7620538848694e-09</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>B_ORDER</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 1, detector to sky</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>B_0_0</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>5.46848630496921e-05</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>B_0_1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0.000544760966309473</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>B_0_2</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>3.78045904395735e-05</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>B_0_3</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>8.38474933780047e-10</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>B_1_0</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>-7.535285644557e-20</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>B_1_1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>-2.5856386119289e-20</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>B_1_2</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>-1.3106781614018e-23</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>B_2_0</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>4.0102324001493e-05</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>B_2_1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>6.04776564999714e-10</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>B_3_0</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>-1.8459105666067e-23</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>AP_ORDER</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 0, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>AP_0_0</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-1.4396838510381e-18</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AP_0_1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>-8.3308084938521e-20</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AP_0_2</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2.07742699238182e-22</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AP_0_3</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>6.19422399713915e-24</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AP_1_0</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1.60796334508681e-05</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AP_1_1</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2.29630963500504e-06</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AP_1_2</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2.54469608202621e-09</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AP_2_0</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1.33765244714635e-22</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AP_2_1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>4.71464037129765e-24</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>AP_3_0</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2.76205388486941e-09</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BP_ORDER</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 1, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BP_0_0</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>-5.4684863049692e-05</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>BP_0_1</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>-0.00054476096630947</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BP_0_2</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>-3.7804590439573e-05</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>BP_0_3</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>-8.3847493378004e-10</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>BP_1_0</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>7.53528564455708e-20</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BP_1_1</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2.5856386119289e-20</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BP_1_2</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1.31067816140184e-23</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BP_2_0</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>-4.0102324001493e-05</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BP_2_1</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>-6.0477656499971e-10</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BP_3_0</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1.84591056660678e-23</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>MODEL_IMAGE</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>MODEL_IMAGE</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1OAE2M9D1MAD1M9D</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:21:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1698318627</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:21:23</t>
+          <t>data unit checksum updated 2026-01-16T15:41:33</t>
         </is>
       </c>
     </row>
@@ -7166,7 +6928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7221,17 +6983,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -7243,17 +7005,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -7269,11 +7031,7 @@
           <t>2048</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7287,299 +7045,131 @@
           <t>2048</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>NAXIS3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>number of parameters</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>APERTURE</t>
-        </is>
-      </c>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONTAM</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>electrons/pixel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Flux not from the target in aperture in e/s</t>
+          <t>data units: electrons/pixel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMPLTE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.8298230297620204</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fraction of flux from the target in aperture</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOTAP</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>582.8889515060163</t>
+          <t>GWiFGVgDGVgDGVgD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Total flux expected in aperture in e/s</t>
+          <t>HDU checksum updated 2026-01-16T15:41:37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>359.98956765457893</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0.01225927433994913</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ROW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1031.0244642272605</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COLUMN</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1958.982650600545</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GAIA_ID</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2738188646457069696</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>9kAICk2I9k9IAk9I</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:21:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:21:23</t>
+          <t>1579659438</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:41:37</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level2_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level2_nirda.xlsx
@@ -17,6 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext6" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext7" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext8" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext9" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext11" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +490,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>ASTROMETRY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -502,12 +505,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CATALOG</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -517,12 +520,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -532,12 +535,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MODEL_IMAGE</t>
+          <t>INTEGRATION</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -547,12 +550,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>VECTORS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C8" t="b">
@@ -562,12 +565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ImageHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C9" t="b">
@@ -577,15 +580,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WAVELENGTH</t>
+          <t>WAVELENGTH_SOLUTION</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TableHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CompImageHDU</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CompImageHDU</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BACKGROUND</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CompImageHDU</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -600,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,17 +681,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TABLE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASCII table extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -700,7 +748,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -718,7 +766,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -771,12 +819,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -793,12 +841,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>wavelength</t>
+          <t>row</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wavelength</t>
+          <t>row</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -811,12 +859,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -830,7 +878,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>micron</t>
+          <t>pix</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -838,17 +886,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TBCOL1</t>
+          <t>TTYPE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>drow</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>drow</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -856,17 +904,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
+          <t>TFORM2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sensitivity</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sensitivity</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -874,17 +922,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D25.17</t>
-        </is>
-      </c>
+          <t>TUNIT2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>D25.17</t>
+          <t>pix</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -892,13 +936,459 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TUNIT2</t>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>wavelength</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wavelength</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TUNIT3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sensitivity</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sensitivity</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TUNIT4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cm2 Angstrom count erg-1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WAVELENGTH_SOLUTION</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>WAVELENGTH_SOLUTION</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Zad4gXZ2Zad2fUZ2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1338844245</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONTAM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.045473326221011905</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Flux not from the target in aperture in e/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>COMPLTE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.0015912325409542</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fraction of flux from the target in aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TOTAP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1325562.8580499147</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Total flux expected in aperture in e/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>316.64702677916716</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-49.96599316312162</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ROW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1086.6741942997198</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COLUMN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cm2 Angstrom electron / (erg pix)</t>
+          <t>1775.28643343575</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -906,17 +1396,13 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TBCOL2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>GAIA_ID</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>6477295296414847232</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -924,58 +1410,1000 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>WAVELENGTH</t>
-        </is>
-      </c>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WAVELENGTH</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>Size of the full detector image in ROW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>IMCRNR0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DPFaENCYDNCaDNCW</t>
+          <t>962</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:41:37</t>
+          <t>Corner of the image in ROW.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>IMSIZE1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3437370878</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:41:37</t>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>97a395T395Z395Z3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>254021566</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>binary table extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of group parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WCSAXES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Number of coordinate axes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CRPIX1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CRPIX2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PC1_1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.94734537413635</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PC1_2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-0.32021358825394</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PC2_1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.32021358825394</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PC2_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-0.94734537413635</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CDELT1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.00033055555555556</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CDELT2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.00033055555555556</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CUNIT1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CUNIT2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CTYPE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RA---TAN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Right ascension, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CTYPE2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEC--TAN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Declination, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CRVAL1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>316.64517211914</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CRVAL2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-49.964656829834</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LONPOLE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[deg] Native longitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LATPOLE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-49.964656829834</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[deg] Native latitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MJDREF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[d] MJD of fiducial time</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RADESYS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Equatorial coordinate system</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MODEL_IMAGE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BGaUBEaUBEaUBEaU</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20259105</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>binary table extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of group parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ct / s</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BACKGROUND</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BACKGROUND</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AQf4CQd1AQd1AQd1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2188102853</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -990,7 +2418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1268,7 +2696,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v2.08</t>
+          <t>v3.06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1304,7 +2732,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1322,7 +2750,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>HD_200654</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1340,7 +2768,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2025/04/05/2025-04-05__13-15-18_InfImg_d2048x2048x0050_b1_e01_i01_g01_d00_r50.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__03-03-20_InfImg_HD_200654_d0080x0250x1583_b1_e01_i427_g02_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1412,7 +2840,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1430,7 +2858,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1466,7 +2894,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1484,7 +2912,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1502,7 +2930,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1538,7 +2966,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1556,7 +2984,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>797174156</t>
+          <t>840078241</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1574,7 +3002,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>738000000</t>
+          <t>877000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1682,7 +3110,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>259</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1718,7 +3146,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1736,7 +3164,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1772,7 +3200,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1790,7 +3218,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1808,7 +3236,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>196</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1898,7 +3326,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1916,7 +3344,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1934,7 +3362,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1952,7 +3380,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1970,7 +3398,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.65685</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1988,7 +3416,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>231</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2006,7 +3434,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>999.0</t>
+          <t>0.5968567132949829</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2024,7 +3452,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>297.6682434082031</t>
+          <t>276.0766906738281</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2042,7 +3470,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>78.88285064697266</t>
+          <t>131.3281707763672</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2060,7 +3488,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>68.87708282470703</t>
+          <t>120.02909851074219</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2078,12 +3506,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9YYe9VXe9VXe9VXe</t>
+          <t>mAaCn0VAm7ZAm7ZA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:41:09</t>
+          <t>HDU checksum updated 2026-08-25T21:26:32</t>
         </is>
       </c>
     </row>
@@ -2101,20 +3529,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:41:09</t>
+          <t>data unit checksum updated 2026-08-25T21:26:32</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0.4.2</t>
+          <t>True</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2122,222 +3550,748 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TARG_RA</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Target right ascension [deg]</t>
-        </is>
-      </c>
+          <t>0.6.0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TARG_DEC</t>
+          <t>PRSOFTV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Target declination [deg]</t>
-        </is>
-      </c>
+          <t>2.9.1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TARG_RLL</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Commanded roll [deg]</t>
-        </is>
-      </c>
+          <t>NIRDALevel2HDUList</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DPCSEQID</t>
+          <t>PFTIME</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2026-08-26T01:26:32.894</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DPC Obseravation Sequence ID</t>
+          <t>Pandora DPC Processing Time</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEQSTART</t>
+          <t>TARG_RA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2454833</t>
+          <t>316.64697265625</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DPC Observation Sequence Start</t>
+          <t>Target right ascension [deg]</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>TARG_DEC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NIRDALevel2HDUList</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>-49.965946197509766</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Target declination [deg]</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PFTIME</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-01-16T22:41:09.242</t>
+          <t>316.6450976892217</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Pandora DPC Processing Time</t>
+          <t>Executed RA [deg]</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GAIA_ID</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2738188646457069696</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>-49.964678241939716</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Executed DEC [deg]</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>ROLL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>108.69678158854717</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Executed roll [deg]</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>POSX</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>1775.4317017434269</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>X [column] Pixel position of target</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>POSY</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>1086.573316065216</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Y [row] Pixel position of target</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIADR3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Gaia DR3 6477295296414847232</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Gaia DR3 source ID</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIARA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>316.64613723994984</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Gaia DR3 RA in J2016</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIADEC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
+          <t>-49.96518470993648</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Gaia DR3 DEC in J2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PARALLAX</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3.621226952307976</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Gaia DR3 parallax</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PMRA</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>193.953457454434</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Gaia DR3 pmra</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PMDEC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>-274.0404188035844</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Gaia DR3 pmdec</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2MASSID</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2MASS J21063474-4957500</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2MASS source ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>J_M</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>7.648</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2MASS j magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>H_M</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>7.252</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2MASS h magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>K_M</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>7.154</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2MASS k magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>G_M</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>8.88517868234036</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Gaia DR3 g magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BP_M</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>9.245725468793857</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Gaia DR3 bp magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>RP_M</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>8.332176759726085</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Gaia DR3 rp magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TEFF</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Gaia DR3 Teff</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>LOGG</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Gaia DR3 logg</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>COLLAPS</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SRT_DATE</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:03:24.877</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>File Start Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>END_DATE</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:24:01.420</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>File End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FILETIME</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>20.609049999999982</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Time the file is observed for in minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>VITLTIME</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>16.61660000681877</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Time VITL was on in minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ONTARG</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>79.59183673469387</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Percentage On Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NKEEPOUT</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>71.42857142857143</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Percentage of time NIRDA keepout obeyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>VKEEPOUT</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>53.06122448979592</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Percentage of time VISDA keepout obeyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>VITLMISS</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>N times VITL return missing data</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>APCOMP1</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>62.33470132238942</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Aperture Completeness Metric 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TARGCENT</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Target Centered</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TARGCOMP</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Target Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TARGTIME</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Usable Target Time is over 10 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DETTEMP</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Detector temperature less than 140K</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Appended Vectors.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2350,7 +4304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2450,7 +4404,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -2464,7 +4418,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -2478,7 +4432,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>196</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -2537,142 +4491,142 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>name of this binary table extension</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>BZERO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KlgjLiehKiehKieh</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:41:21</t>
-        </is>
-      </c>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4085838779</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:41:21</t>
-        </is>
-      </c>
+          <t>ct / s</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>electrons/pixel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data units: electrons/pixel</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.4.2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>1781.0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Number of coordinate axes</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2008.0</t>
+          <t>-0.94722828568499</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CRPIX2</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>-0.32055978350112</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PC1_1</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.76604444311898</t>
+          <t>0.32055978350112</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2684,13 +4638,13 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PC1_2</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
+          <t>-0.94722828568499</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2702,1044 +4656,594 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PC2_1</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
+          <t>0.00033055555555556</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PC2_2</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.76604444311898</t>
+          <t>0.00033055555555556</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CDELT1</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.00033055555555555</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[deg] Coordinate increment at reference point</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CDELT2</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.00033055555555556</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[deg] Coordinate increment at reference point</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CUNIT1</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>RA---TAN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>Right ascension, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CUNIT2</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>DEC--TAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>Declination, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CTYPE1</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RA---TAN-SIP</t>
+          <t>316.64509768922</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CTYPE2</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DEC--TAN-SIP</t>
+          <t>-49.96467824194</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRVAL1</t>
+          <t>LONPOLE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>[deg] Native longitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CRVAL2</t>
+          <t>LATPOLE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-49.96467824194</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>[deg] Native latitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LONPOLE</t>
+          <t>MJDREF</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[deg] Native longitude of celestial pole</t>
+          <t>[d] MJD of fiducial time</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LATPOLE</t>
+          <t>RADESYS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>ICRS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[deg] Native latitude of celestial pole</t>
+          <t>Equatorial coordinate system</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MJDREF</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[d] MJD of fiducial time</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RADESYS</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ICRS</t>
+          <t>1781.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Equatorial coordinate system</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A_ORDER</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 0, detector to sky</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A_0_0</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.43968385103818e-18</t>
+          <t>-0.94734537413635</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A_0_1</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8.33080849385211e-20</t>
+          <t>-0.32021358825394</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A_0_2</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-2.0774269923818e-22</t>
+          <t>0.32021358825394</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A_0_3</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-6.1942239971391e-24</t>
+          <t>-0.94734537413635</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A_1_0</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-1.6079633450868e-05</t>
+          <t>0.00033055555555556</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A_1_1</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-2.296309635005e-06</t>
+          <t>0.00033055555555556</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A_1_2</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-2.5446960820262e-09</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A_2_0</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-1.3376524471463e-22</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A_2_1</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-4.7146403712976e-24</t>
+          <t>RA---TAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Right ascension, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A_3_0</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-2.7620538848694e-09</t>
+          <t>DEC--TAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Declination, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B_ORDER</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>316.64517211914</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 1, detector to sky</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B_0_0</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5.46848630496921e-05</t>
+          <t>-49.964656829834</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B_0_1</t>
+          <t>LONPOLE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.000544760966309473</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Native longitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B_0_2</t>
+          <t>LATPOLE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3.78045904395735e-05</t>
+          <t>-49.964656829834</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[deg] Native latitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B_0_3</t>
+          <t>MJDREF</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8.38474933780047e-10</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>[d] MJD of fiducial time</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B_1_0</t>
+          <t>RADESYS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-7.535285644557e-20</t>
+          <t>ICRS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Equatorial coordinate system</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B_1_1</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-2.5856386119289e-20</t>
+          <t>YXipaWZoSWfoYWZo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>HDU checksum updated 2026-08-25T21:26:33</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B_1_2</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-1.3106781614018e-23</t>
+          <t>2162534189</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>B_2_0</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>4.0102324001493e-05</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>B_2_1</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>6.04776564999714e-10</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>B_3_0</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>-1.8459105666067e-23</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AP_ORDER</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 0, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AP_0_0</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>-1.4396838510381e-18</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AP_0_1</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>-8.3308084938521e-20</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AP_0_2</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2.07742699238182e-22</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>AP_0_3</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>6.19422399713915e-24</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>AP_1_0</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1.60796334508681e-05</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>AP_1_1</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2.29630963500504e-06</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>AP_1_2</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2.54469608202621e-09</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>AP_2_0</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1.33765244714635e-22</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>AP_2_1</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>4.71464037129765e-24</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>AP_3_0</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2.76205388486941e-09</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BP_ORDER</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 1, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BP_0_0</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>-5.4684863049692e-05</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BP_0_1</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>-0.00054476096630947</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BP_0_2</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>-3.7804590439573e-05</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BP_0_3</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>-8.3847493378004e-10</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BP_1_0</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>7.53528564455708e-20</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>BP_1_1</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2.5856386119289e-20</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BP_1_2</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1.31067816140184e-23</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>BP_2_0</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>-4.0102324001493e-05</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BP_2_1</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>-6.0477656499971e-10</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>BP_3_0</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1.84591056660678e-23</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
+          <t>data unit checksum updated 2026-08-25T21:26:33</t>
         </is>
       </c>
     </row>
@@ -3754,7 +5258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3787,17 +5291,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -3809,17 +5313,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -3841,7 +5345,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -3854,12 +5358,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 1</t>
         </is>
       </c>
     </row>
@@ -3872,12 +5376,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 2</t>
         </is>
       </c>
     </row>
@@ -3895,7 +5399,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -3920,35 +5424,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSCALE</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BZERO</t>
+          <t>TTYPE1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -3956,58 +5464,216 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFORM1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RightAscension</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>J9ahJ9WfJ9afJ9Wf</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:41:24</t>
-        </is>
-      </c>
+          <t>RightAscension</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PCOTemp</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PCOTemp</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OZAMRX4LOX9LOX9L</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4292739037</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:41:24</t>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2712404471</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -4022,7 +5688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4055,17 +5721,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -4077,12 +5743,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4099,12 +5765,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4122,646 +5788,120 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>FRAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Time frame is JD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>5BME79J95AJC57J9</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TTYPE6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TFORM6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TTYPE7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TFORM7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TTYPE8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TFORM8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TTYPE9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TFORM9</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TTYPE10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TFORM10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TTYPE11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TFORM11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TTYPE12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TFORM12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TTYPE13</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TFORM13</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TTYPE14</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TFORM14</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Zb6Rea4RZa4Rda4R</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:41:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>3727981219</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:41:24</t>
+          <t>795823793</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -4776,7 +5916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4841,7 +5981,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -4853,17 +5993,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -4876,178 +6016,120 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAXIS3</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>second</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>Exposure time unit</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EXPTIME</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PRF_MODEL</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>gafjgRcggXcggXcg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DPOS0</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4016947927</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Change in position in Row from original WCS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DPOS1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Change in position in Column from original WCS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>5AiDA1gC78gCA8gC</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:41:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3098569257</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:41:33</t>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -5062,7 +6144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5105,7 +6187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -5117,17 +6199,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -5139,17 +6221,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -5162,1330 +6244,102 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INTEGRATION</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>INTEGRATION</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9Wa8FUS89UY8CUY8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Number of coordinate axes</t>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2008.0</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CRPIX2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1024.0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PC1_1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-0.76604444311898</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PC1_2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-0.64278760968654</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PC2_1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>-0.64278760968654</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PC2_2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0.76604444311898</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Coordinate transformation matrix element</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CDELT1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-0.00033055555555555</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CDELT2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0.00033055555555556</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate increment at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CUNIT1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CUNIT2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Units of coordinate increment and value</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CTYPE1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>RA---TAN-SIP</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CTYPE2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DEC--TAN-SIP</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CRVAL1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CRVAL2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[deg] Coordinate value at reference point</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LONPOLE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[deg] Native longitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LATPOLE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>[deg] Native latitude of celestial pole</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MJDREF</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>[d] MJD of fiducial time</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RADESYS</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ICRS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Equatorial coordinate system</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A_ORDER</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 0, detector to sky</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A_0_0</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1.43968385103818e-18</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A_0_1</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>8.33080849385211e-20</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A_0_2</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-2.0774269923818e-22</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A_0_3</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>-6.1942239971391e-24</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A_1_0</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-1.6079633450868e-05</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A_1_1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-2.296309635005e-06</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A_1_2</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>-2.5446960820262e-09</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A_2_0</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-1.3376524471463e-22</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A_2_1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>-4.7146403712976e-24</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A_3_0</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-2.7620538848694e-09</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>B_ORDER</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 1, detector to sky</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>B_0_0</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>5.46848630496921e-05</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>B_0_1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0.000544760966309473</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>B_0_2</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>3.78045904395735e-05</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>B_0_3</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>8.38474933780047e-10</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>B_1_0</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>-7.535285644557e-20</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>B_1_1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>-2.5856386119289e-20</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>B_1_2</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>-1.3106781614018e-23</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>B_2_0</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>4.0102324001493e-05</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>B_2_1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>6.04776564999714e-10</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>B_3_0</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>-1.8459105666067e-23</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>AP_ORDER</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 0, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>AP_0_0</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-1.4396838510381e-18</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AP_0_1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>-8.3308084938521e-20</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AP_0_2</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2.07742699238182e-22</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AP_0_3</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>6.19422399713915e-24</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AP_1_0</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1.60796334508681e-05</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AP_1_1</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2.29630963500504e-06</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AP_1_2</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2.54469608202621e-09</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AP_2_0</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1.33765244714635e-22</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AP_2_1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>4.71464037129765e-24</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>AP_3_0</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2.76205388486941e-09</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BP_ORDER</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SIP polynomial order, axis 1, sky to detector</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BP_0_0</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>-5.4684863049692e-05</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>BP_0_1</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>-0.00054476096630947</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BP_0_2</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>-3.7804590439573e-05</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>BP_0_3</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>-8.3847493378004e-10</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>BP_1_0</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>7.53528564455708e-20</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BP_1_1</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2.5856386119289e-20</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BP_1_2</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1.31067816140184e-23</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BP_2_0</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>-4.0102324001493e-05</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BP_2_1</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>-6.0477656499971e-10</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BP_3_0</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1.84591056660678e-23</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>SIP distortion coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>MODEL_IMAGE</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>MODEL_IMAGE</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1NBD1K9B1KAB1K7B</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:41:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1698318627</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:41:33</t>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6533,17 +6387,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -6555,17 +6409,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6441,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -6600,12 +6454,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 1</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6472,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>196</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 2</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6495,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -6666,89 +6520,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>number of table fields</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONTAM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>TTYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avg_ra</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Flux not from the target in aperture in e/s</t>
-        </is>
-      </c>
+          <t>avg_ra</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMPLTE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.8298230297620204</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fraction of flux from the target in aperture</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOTAP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avg_dec</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>582.8889515060163</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Total flux expected in aperture in e/s</t>
-        </is>
-      </c>
+          <t>avg_dec</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>359.98956765457893</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -6756,13 +6614,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avg_rot</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.01225927433994913</t>
+          <t>avg_rot</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -6770,13 +6632,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ROW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1031.0244642272605</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -6784,13 +6650,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COLUMN</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>err_ra</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1958.982650600545</t>
+          <t>err_ra</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -6798,13 +6668,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GAIA_ID</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2738188646457069696</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -6812,108 +6686,558 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>err_dec</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
+          <t>err_dec</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>err_rot</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
+          <t>err_rot</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>jd</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9j9HBi9G9i9GAi9G</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T15:41:33</t>
-        </is>
-      </c>
+          <t>jd</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>exptime</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>exptime</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>target_sep</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>target_sep</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>vitl_frames_count</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>vitl_frames_count</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>vitl_missing_frames</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>vitl_missing_frames</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TTYPE14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TFORM14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TTYPE15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TFORM15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TTYPE16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TFORM16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TTYPE17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TFORM17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TTYPE18</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TFORM18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7HeBB9ZB9EbBA9ZB</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T15:41:33</t>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1005148229</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -6983,17 +7307,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -7005,17 +7329,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -7028,10 +7352,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7042,78 +7370,86 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAXIS3</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>BSCALE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>BZERO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>electrons/pixel</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>data units: electrons/pixel</t>
-        </is>
-      </c>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7123,12 +7459,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7146,12 +7482,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GWiFGVgDGVgDGVgD</t>
+          <t>97alH4Vi94aiG4Ui</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:41:37</t>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -7164,12 +7500,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1579659438</t>
+          <t>335287306</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:41:37</t>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level2_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level2_nirda.xlsx
@@ -1060,12 +1060,12 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Zad4gXZ2Zad2fUZ2</t>
+          <t>aag3aVZ1aZd1aZZ1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>97a395T395Z395Z3</t>
+          <t>96a2A4U244a294U2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BGaUBEaUBEaUBEaU</t>
+          <t>BFdTEDaTBDaTBDaT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -2380,12 +2380,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AQf4CQd1AQd1AQd1</t>
+          <t>BPf3CPe0BPe0BPe0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3506,12 +3506,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mAaCn0VAm7ZAm7ZA</t>
+          <t>nAeeq8ZbnAbbn5Zb</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:32</t>
+          <t>HDU checksum updated 2026-09-08T14:41:32</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:32</t>
+          <t>data unit checksum updated 2026-09-08T14:41:32</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-26T01:26:32.894</t>
+          <t>2026-09-08T18:41:32.828</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4236,62 +4236,134 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DETTEMP</t>
+          <t>BKG10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>95.45454545454545</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Detector temperature less than 140K</t>
+          <t>10th percentile of Background</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>BKG50</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>103.24675324675324</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>50th percentile of Background</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>BKG90</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Appended Vectors.</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>1823.6471861471853</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>90th percentile of Background</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>DETTEMP1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Cold Tip 1 temperature less than 140K</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DETTEMP2</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Cold Tip 2 temperature less than 140K</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Appended Vectors.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5220,12 +5292,12 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YXipaWZoSWfoYWZo</t>
+          <t>ZWcoaVanTVanZVan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:33</t>
+          <t>HDU checksum updated 2026-09-08T14:41:33</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5315,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:33</t>
+          <t>data unit checksum updated 2026-09-08T14:41:33</t>
         </is>
       </c>
     </row>
@@ -5650,12 +5722,12 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OZAMRX4LOX9LOX9L</t>
+          <t>PYALRW5KPWAKPW3K</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5745,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -5878,12 +5950,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5BME79J95AJC57J9</t>
+          <t>6AMC78K96AKA65K9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5973,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -6106,12 +6178,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gafjgRcggXcggXcg</t>
+          <t>gZfijWdfgWdfgWdf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6201,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6388,12 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9Wa8FUS89UY8CUY8</t>
+          <t>9Va7GTT79TZ7ETZ7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6411,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7286,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>7HeBB9ZB9EbBA9ZB</t>
+          <t>9FfAC9ZA9CdAA9ZA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7309,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -7482,12 +7554,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>97alH4Vi94aiG4Ui</t>
+          <t>A6akA3WhA3ahA3Wh</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7577,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level2_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level2_nirda.xlsx
@@ -1060,12 +1060,12 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>aag3aVZ1aZd1aZZ1</t>
+          <t>9M5MFM5K9M5KEM5K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1338844245</t>
+          <t>2322579671</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.045473326221011905</t>
+          <t>1.45948781805724e-05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1310,7 +1310,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0015912325409542</t>
+          <t>1.0001196545262074</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1328,7 +1328,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1325562.8580499147</t>
+          <t>6054546.661906874</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>316.64702677916716</t>
+          <t>307.85996711980397</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-49.96599316312162</t>
+          <t>39.93898084328189</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1086.6741942997198</t>
+          <t>1086.4587761921186</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1388,7 +1388,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1775.28643343575</t>
+          <t>1775.530593149113</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1402,7 +1402,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6477295296414847232</t>
+          <t>2064327278651198336</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1488,12 +1488,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>96a2A4U244a294U2</t>
+          <t>eD6kf93ieC3ie93i</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>254021566</t>
+          <t>178391814</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.94734537413635</t>
+          <t>0.92523789004974</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>-0.3793874626504</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1788,7 +1788,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.32021358825394</t>
+          <t>0.3793874626504</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1806,7 +1806,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.94734537413635</t>
+          <t>0.92523789004974</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1932,7 +1932,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>316.64517211914</t>
+          <t>307.86215209961</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1950,7 +1950,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1986,7 +1986,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2134,12 +2134,12 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BFdTEDaTBDaTBDaT</t>
+          <t>LF7VOD4VLD4VLD4V</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2152,12 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20259105</t>
+          <t>4243662291</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2380,12 +2380,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BPf3CPe0BPe0BPe0</t>
+          <t>a0AUc06Ta0ATa03T</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2398,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2188102853</t>
+          <t>4262218308</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HD_200654</t>
+          <t>KELT-9b</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2768,7 +2768,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/08/15/2026-08-15__03-03-20_InfImg_HD_200654_d0080x0250x1583_b1_e01_i427_g02_d16_r04.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__06-44-18_InfImg_KELT-9b_d0080x0250x3096_b1_e01_i387_g02_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>774</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2984,7 +2984,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>840078241</t>
+          <t>840091495</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3002,7 +3002,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>877000000</t>
+          <t>832000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3236,7 +3236,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3326,7 +3326,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3344,7 +3344,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3362,7 +3362,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3434,7 +3434,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.5968567132949829</t>
+          <t>3.3816466331481934</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3452,7 +3452,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>276.0766906738281</t>
+          <t>278.990966796875</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3470,7 +3470,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>131.3281707763672</t>
+          <t>131.50372314453125</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3488,7 +3488,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>120.02909851074219</t>
+          <t>120.03438568115234</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3506,12 +3506,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>nAeeq8ZbnAbbn5Zb</t>
+          <t>9agDGWgC9agCEWgC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:32</t>
+          <t>HDU checksum updated 2026-09-09T15:46:08</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:32</t>
+          <t>data unit checksum updated 2026-09-09T15:46:08</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-08T18:41:32.828</t>
+          <t>2026-09-09T19:46:08.484</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3616,7 +3616,7 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>316.64697265625</t>
+          <t>307.8599548339844</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3634,7 +3634,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-49.965946197509766</t>
+          <t>39.9389762878418</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3652,7 +3652,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>316.6450976892217</t>
+          <t>307.86216741569376</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3670,7 +3670,7 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>-49.964678241939716</t>
+          <t>39.93878532835476</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3688,7 +3688,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>108.69678158854717</t>
+          <t>247.7078167885557</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3706,7 +3706,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1775.4317017434269</t>
+          <t>1775.498998065344</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3724,7 +3724,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1086.573316065216</t>
+          <t>1086.4568375724239</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3742,7 +3742,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gaia DR3 6477295296414847232</t>
+          <t>Gaia DR3 2064327278651198336</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3760,7 +3760,7 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>316.64613723994984</t>
+          <t>307.8599027970418</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3778,7 +3778,7 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-49.96518470993648</t>
+          <t>39.93891900336815</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3796,7 +3796,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3.621226952307976</t>
+          <t>4.825836101438949</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3814,7 +3814,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>193.953457454434</t>
+          <t>16.716578051403854</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3832,7 +3832,7 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-274.0404188035844</t>
+          <t>20.96090596020299</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3850,7 +3850,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2MASS J21063474-4957500</t>
+          <t>2MASS J20312634+3956196</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3868,7 +3868,7 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>7.648</t>
+          <t>7.458</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3886,7 +3886,7 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>7.252</t>
+          <t>7.492</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3904,7 +3904,7 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>7.154</t>
+          <t>7.482</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3922,7 +3922,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>8.88517868234036</t>
+          <t>7.5902658552584015</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3940,7 +3940,7 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9.245725468793857</t>
+          <t>7.594925828938212</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3958,7 +3958,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>8.332176759726085</t>
+          <t>7.552309075270038</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3976,7 +3976,7 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9951.392</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3994,7 +3994,7 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.9497</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4020,198 +4020,198 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SRT_DATE</t>
+          <t>BKG10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-15T03:03:24.877</t>
+          <t>119.15584415584416</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>File Start Date</t>
+          <t>10th percentile of Background</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>END_DATE</t>
+          <t>BKG50</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-15T03:24:01.420</t>
+          <t>157.034632034632</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>File End Date</t>
+          <t>50th percentile of Background</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FILETIME</t>
+          <t>BKG90</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>20.609049999999982</t>
+          <t>188.3116883116883</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Time the file is observed for in minutes</t>
+          <t>90th percentile of Background</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VITLTIME</t>
+          <t>SRT_DATE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>16.61660000681877</t>
+          <t>2026-08-15T06:44:18.832</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Time VITL was on in minutes</t>
+          <t>File Start Date</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ONTARG</t>
+          <t>END_DATE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>79.59183673469387</t>
+          <t>2026-08-15T07:24:02.752</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Percentage On Target</t>
+          <t>File End Date</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NKEEPOUT</t>
+          <t>FILETIME</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>71.42857142857143</t>
+          <t>39.73200000000002</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Percentage of time NIRDA keepout obeyed</t>
+          <t>Time the file is observed for in minutes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VKEEPOUT</t>
+          <t>VITLTIME</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>53.06122448979592</t>
+          <t>38.638600185513496</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Percentage of time VISDA keepout obeyed</t>
+          <t>Time VITL was on in minutes</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VITLMISS</t>
+          <t>ONTARG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>N times VITL return missing data</t>
+          <t>Percentage On Target</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>APCOMP1</t>
+          <t>NKEEPOUT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>62.33470132238942</t>
+          <t>48.320413436692505</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aperture Completeness Metric 1</t>
+          <t>Percentage of time NIRDA keepout obeyed</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TARGCENT</t>
+          <t>VKEEPOUT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>21.44702842377261</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Target Centered</t>
+          <t>Percentage of time VISDA keepout obeyed</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TARGCOMP</t>
+          <t>VITLMISS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Target Complete</t>
+          <t>N times VITL return missing data</t>
         </is>
       </c>
     </row>
@@ -4236,54 +4236,54 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BKG10</t>
+          <t>APCOMP1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>95.45454545454545</t>
+          <t>94.34050514499532</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10th percentile of Background</t>
+          <t>Aperture Completeness Metric 1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BKG50</t>
+          <t>TARGCENT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>103.24675324675324</t>
+          <t>True</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>50th percentile of Background</t>
+          <t>Target Centered</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BKG90</t>
+          <t>TARGCOMP</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1823.6471861471853</t>
+          <t>True</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>90th percentile of Background</t>
+          <t>Target Complete</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,7 +4504,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -4563,88 +4563,88 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>name of this binary table extension</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BZERO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>32768</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>32768</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>haAkkY7khaAkhY5k</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-09-09T15:46:10</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ct / s</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>1725050178</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-09-09T15:46:10</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Number of coordinate axes</t>
-        </is>
-      </c>
+          <t>ct / s</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1781.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CRPIX2</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>1781.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4656,31 +4656,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PC1_1</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.94722828568499</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PC1_2</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.32055978350112</t>
+          <t>0.92526147848475</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4692,13 +4692,13 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PC2_1</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.32055978350112</t>
+          <t>-0.37932993084148</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4710,13 +4710,13 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PC2_2</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.94722828568499</t>
+          <t>0.37932993084148</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4728,25 +4728,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CDELT1</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.00033055555555556</t>
+          <t>0.92526147848475</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[deg] Coordinate increment at reference point</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CDELT2</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -4764,25 +4764,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CUNIT1</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>0.00033055555555556</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CUNIT2</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -4800,67 +4800,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CTYPE1</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RA---TAN</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Right ascension, gnomonic projection</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CTYPE2</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DEC--TAN</t>
+          <t>RA---TAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Declination, gnomonic projection</t>
+          <t>Right ascension, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CRVAL1</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>316.64509768922</t>
+          <t>DEC--TAN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>Declination, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRVAL2</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-49.96467824194</t>
+          <t>307.86216741569</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4872,121 +4872,121 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LONPOLE</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>39.938785328355</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[deg] Native longitude of celestial pole</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LATPOLE</t>
+          <t>LONPOLE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-49.96467824194</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[deg] Native latitude of celestial pole</t>
+          <t>[deg] Native longitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MJDREF</t>
+          <t>LATPOLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.938785328355</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[d] MJD of fiducial time</t>
+          <t>[deg] Native latitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RADESYS</t>
+          <t>MJDREF</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ICRS</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Equatorial coordinate system</t>
+          <t>[d] MJD of fiducial time</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
+          <t>RADESYS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ICRS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Number of coordinate axes</t>
+          <t>Equatorial coordinate system</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1781.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CRPIX2</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>1781.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4998,31 +4998,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PC1_1</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-0.94734537413635</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PC1_2</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-0.32021358825394</t>
+          <t>0.92523789004974</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5034,13 +5034,13 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PC2_1</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.32021358825394</t>
+          <t>-0.3793874626504</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5052,13 +5052,13 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PC2_2</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-0.94734537413635</t>
+          <t>0.3793874626504</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5070,25 +5070,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CDELT1</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.00033055555555556</t>
+          <t>0.92523789004974</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[deg] Coordinate increment at reference point</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDELT2</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -5106,25 +5106,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CUNIT1</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>0.00033055555555556</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CUNIT2</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -5142,67 +5142,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CTYPE1</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RA---TAN</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Right ascension, gnomonic projection</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CTYPE2</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DEC--TAN</t>
+          <t>RA---TAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Declination, gnomonic projection</t>
+          <t>Right ascension, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CRVAL1</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>316.64517211914</t>
+          <t>DEC--TAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>Declination, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CRVAL2</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>307.86215209961</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5214,108 +5214,90 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LONPOLE</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[deg] Native longitude of celestial pole</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LATPOLE</t>
+          <t>LONPOLE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-49.964656829834</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[deg] Native latitude of celestial pole</t>
+          <t>[deg] Native longitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MJDREF</t>
+          <t>LATPOLE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.938789367676</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[d] MJD of fiducial time</t>
+          <t>[deg] Native latitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RADESYS</t>
+          <t>MJDREF</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ICRS</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Equatorial coordinate system</t>
+          <t>[d] MJD of fiducial time</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>RADESYS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ZWcoaVanTVanZVan</t>
+          <t>ICRS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2162534189</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-09-08T14:41:33</t>
+          <t>Equatorial coordinate system</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5430,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5722,12 +5704,12 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PYALRW5KPWAKPW3K</t>
+          <t>3UTa3SQY3SQa3SQY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5722,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2712404471</t>
+          <t>3190933090</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5842,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5950,12 +5932,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6AMC78K96AKA65K9</t>
+          <t>0He51Hc40Hc40Hc4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -5968,12 +5950,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>795823793</t>
+          <t>4194533316</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6070,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -6178,12 +6160,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gZfijWdfgWdfgWdf</t>
+          <t>bKAlcI7kbIAkbI5k</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6178,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4016947927</t>
+          <t>941144289</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6298,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -6388,12 +6370,12 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9Va7GTT79TZ7ETZ7</t>
+          <t>5XYF5VW95VWE5VW9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -6406,12 +6388,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>74691</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6526,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7286,12 +7268,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9FfAC9ZA9CdAA9ZA</t>
+          <t>nIJ7pHJ5nHJ5nHJ5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7286,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1005148229</t>
+          <t>708805240</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7536,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A6akA3WhA3ahA3Wh</t>
+          <t>95ajG4Ui94aiG4Ui</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7559,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:12</t>
         </is>
       </c>
     </row>
